--- a/01_Risk_Management/GRC_Risk_Register_R001.xlsx
+++ b/01_Risk_Management/GRC_Risk_Register_R001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/90cd24471badb8ba/Documentos/CYBER SECURITY JULIETH/PROYECTO 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="8_{60FF319E-0215-4697-86C0-21D4FF0F5B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50A2D852-84EC-49D4-AFE3-1F3B765AE974}"/>
+  <xr:revisionPtr revIDLastSave="141" documentId="8_{60FF319E-0215-4697-86C0-21D4FF0F5B35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20431CCB-6009-491A-8C3F-ECF8EB608CF8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{B289C43C-255F-4056-A5BC-44598FD46C3C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{B289C43C-255F-4056-A5BC-44598FD46C3C}"/>
   </bookViews>
   <sheets>
     <sheet name="GRC_Risk_Register" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="63">
   <si>
     <t>Risk ID</t>
   </si>
@@ -139,13 +139,105 @@
   </si>
   <si>
     <t>The controls reduce the likelihood of unauthorized access, but the risk cannot be completely eliminated because users may still fall victim to phishing or misuse their credentials.</t>
+  </si>
+  <si>
+    <t>R-002</t>
+  </si>
+  <si>
+    <t>A-003: Financial Information and Invoices</t>
+  </si>
+  <si>
+    <t>Unauthorized access and invoice modification through a compromised account</t>
+  </si>
+  <si>
+    <t>Potential weak passwords or insufficient access controls; pending verification</t>
+  </si>
+  <si>
+    <t>High (provisional, based on the exercise)</t>
+  </si>
+  <si>
+    <t>High (provisional, according to the rating scale used)</t>
+  </si>
+  <si>
+    <t>To be determined after control assessment</t>
+  </si>
+  <si>
+    <t>C-03 — Invoice Modification Logging. Effectiveness pending confirmation; traceability exception pending investigation in the hypothetical scenario.</t>
+  </si>
+  <si>
+    <t>To be assigned or confirmed</t>
+  </si>
+  <si>
+    <t>Pending assessment; the exception must be investigated and control effectiveness verified.</t>
+  </si>
+  <si>
+    <t>R-001 -Exercise Customer financial information</t>
+  </si>
+  <si>
+    <t>R-002 — Project 1: Invoice Modification Risk</t>
+  </si>
+  <si>
+    <t>Risk ID:</t>
+  </si>
+  <si>
+    <t>Asset:</t>
+  </si>
+  <si>
+    <t>A-003 — Financial Information and Invoices</t>
+  </si>
+  <si>
+    <t>High (provisional)</t>
+  </si>
+  <si>
+    <t>The hypothetical risk scenario involves unauthorized invoice modification through a compromised employee account. Potential weaknesses incluide weak passwords or insufficient access controls; these have not been verified in the SME.
+The initial likelihood and impact ratings are provisional and must be validated against the established risk assessment criteria.</t>
+  </si>
+  <si>
+    <t>To be determined after further control assessment.</t>
+  </si>
+  <si>
+    <t>1. C-03- Invoice modification logging (proposed control; implementation and effectiveness not verified)</t>
+  </si>
+  <si>
+    <t>2. C-01 - Restricted access to invoice modification (candidate control; implementation not verified)</t>
+  </si>
+  <si>
+    <t>3. C-02 - Multi-factor authentication (candidate control; implementation not verified).</t>
+  </si>
+  <si>
+    <t>Pending assessment.</t>
+  </si>
+  <si>
+    <t>The effectiveness of the proposed logging control has not been confirmed. In the hypothetical test scenario, one of the reviewed invoice modifications lacked user identification. The cause and significance of this excepción requiere further investigation.
+The residual risk rating will remain pending until the exception is investigated and the relevant preventive and detective controls are evaliated.</t>
+  </si>
+  <si>
+    <t>Next Steps:</t>
+  </si>
+  <si>
+    <t>1. Investigate the cause of the missing user identification.</t>
+  </si>
+  <si>
+    <t>2. Verify the completeness and consistency of the modification logs.</t>
+  </si>
+  <si>
+    <t>3. Assess the implementation and effectiveness of relevant controls.</t>
+  </si>
+  <si>
+    <t>4. Reassess residual likelihood and impact using the established risk-rating criteria.</t>
+  </si>
+  <si>
+    <t>Note:</t>
+  </si>
+  <si>
+    <t>This is a hypothetical  learning exercise and does not represent verified findings about the SME.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,6 +249,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -194,7 +293,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -337,11 +436,91 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -373,15 +552,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -391,19 +561,56 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,6 +632,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -744,78 +955,116 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{544FAC52-2EC6-4014-9522-68A9CEE99545}">
-  <dimension ref="B1:L3"/>
+  <dimension ref="B1:L4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="12" width="19.5546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="I2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="16" t="s">
+      <c r="L2" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="17" t="s">
+    <row r="3" spans="2:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="7" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="B4" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -825,182 +1074,851 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE37528A-2930-4B20-B5E7-C222B8B3DCBA}">
-  <dimension ref="B1:G34"/>
+  <dimension ref="C1:R46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.109375" customWidth="1"/>
+    <col min="1" max="3" width="4.88671875" customWidth="1"/>
+    <col min="4" max="4" width="24.109375" customWidth="1"/>
+    <col min="10" max="12" width="5.109375" customWidth="1"/>
+    <col min="13" max="13" width="24.109375" customWidth="1"/>
+    <col min="14" max="16" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="1" t="s">
+    <row r="1" spans="3:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C2" s="23"/>
+      <c r="D2" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="26"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="38"/>
+    </row>
+    <row r="3" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C3" s="27"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="28"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="28"/>
+    </row>
+    <row r="4" spans="3:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C4" s="27"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="28"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="28"/>
+    </row>
+    <row r="5" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C5" s="27"/>
+      <c r="D5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="5" t="s">
+      <c r="H5" s="17"/>
+      <c r="I5" s="28"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="O5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q5" s="17"/>
+      <c r="R5" s="28"/>
+    </row>
+    <row r="6" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C6" s="27"/>
+      <c r="D6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B4" s="8" t="s">
+      <c r="H6" s="17"/>
+      <c r="I6" s="28"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="Q6" s="17"/>
+      <c r="R6" s="28"/>
+    </row>
+    <row r="7" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C7" s="27"/>
+      <c r="D7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="F7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="9" t="s">
+      <c r="H7" s="17"/>
+      <c r="I7" s="28"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="P7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="Q7" s="17"/>
+      <c r="R7" s="28"/>
+    </row>
+    <row r="8" spans="3:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="27"/>
+      <c r="D8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="F8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="G8" s="15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="18" t="s">
+      <c r="H8" s="17"/>
+      <c r="I8" s="28"/>
+      <c r="L8" s="27"/>
+      <c r="M8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="P8" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="28"/>
+    </row>
+    <row r="9" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C9" s="27"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="28"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="28"/>
+    </row>
+    <row r="10" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C10" s="27"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="28"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="N10" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="28"/>
+    </row>
+    <row r="11" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C11" s="27"/>
+      <c r="D11" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="E11" s="19" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="18" t="s">
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="28"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="N11" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="O11" s="35"/>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="28"/>
+    </row>
+    <row r="12" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C12" s="27"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="28"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="28"/>
+    </row>
+    <row r="13" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C13" s="27"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="28"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="N13" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="28"/>
+    </row>
+    <row r="14" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C14" s="27"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="28"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="28"/>
+    </row>
+    <row r="15" spans="3:18" ht="107.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="27"/>
+      <c r="D15" s="18" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="18"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="28"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="O15" s="22"/>
+      <c r="P15" s="22"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="28"/>
+    </row>
+    <row r="16" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C16" s="27"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+      <c r="I16" s="28"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17"/>
+      <c r="R16" s="28"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C17" s="27"/>
+      <c r="D17" s="17" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="12" t="s">
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="28"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="Q17" s="17"/>
+      <c r="R17" s="28"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C18" s="27"/>
+      <c r="D18" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="18" t="s">
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="29"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="29"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C19" s="27"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="29"/>
+      <c r="L19" s="27"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="20"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="20"/>
+      <c r="Q19" s="20"/>
+      <c r="R19" s="29"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C20" s="27"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="28"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="17"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17"/>
+      <c r="R20" s="28"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C21" s="27"/>
+      <c r="D21" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C18" t="s">
+      <c r="E21" s="17" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B21" s="18" t="s">
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="28"/>
+      <c r="L21" s="27"/>
+      <c r="M21" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="Q21" s="17"/>
+      <c r="R21" s="28"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C22" s="27"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="28"/>
+      <c r="L22" s="27"/>
+      <c r="M22" s="17"/>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="28"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C23" s="27"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="28"/>
+      <c r="L23" s="27"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="28"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C24" s="27"/>
+      <c r="D24" s="18" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B22" s="18"/>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="28"/>
+      <c r="L24" s="27"/>
+      <c r="M24" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" s="17"/>
+      <c r="O24" s="17"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="28"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C25" s="27"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="28"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="28"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C26" s="27"/>
+      <c r="D26" s="17" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="28"/>
+      <c r="L26" s="27"/>
+      <c r="M26" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="28"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C27" s="27"/>
+      <c r="D27" s="17" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="28"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="N27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="28"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C28" s="27"/>
+      <c r="D28" s="17" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B28" s="18" t="s">
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="28"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="N28" s="17"/>
+      <c r="O28" s="17"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="28"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C29" s="27"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="28"/>
+      <c r="L29" s="27"/>
+      <c r="M29" s="17"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="Q29" s="17"/>
+      <c r="R29" s="28"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C30" s="27"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="28"/>
+      <c r="L30" s="27"/>
+      <c r="M30" s="17"/>
+      <c r="N30" s="17"/>
+      <c r="O30" s="17"/>
+      <c r="P30" s="17"/>
+      <c r="Q30" s="17"/>
+      <c r="R30" s="28"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C31" s="27"/>
+      <c r="D31" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="E31" s="21" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B31" s="18" t="s">
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="28"/>
+      <c r="L31" s="27"/>
+      <c r="M31" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="N31" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="Q31" s="17"/>
+      <c r="R31" s="28"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C32" s="27"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="28"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="17"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
+      <c r="P32" s="17"/>
+      <c r="Q32" s="17"/>
+      <c r="R32" s="28"/>
+    </row>
+    <row r="33" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C33" s="27"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="28"/>
+      <c r="L33" s="27"/>
+      <c r="M33" s="17"/>
+      <c r="N33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="Q33" s="17"/>
+      <c r="R33" s="28"/>
+    </row>
+    <row r="34" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C34" s="27"/>
+      <c r="D34" s="18" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B32" s="13" t="s">
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="28"/>
+      <c r="L34" s="27"/>
+      <c r="M34" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="N34" s="17"/>
+      <c r="O34" s="17"/>
+      <c r="P34" s="17"/>
+      <c r="Q34" s="17"/>
+      <c r="R34" s="28"/>
+    </row>
+    <row r="35" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C35" s="27"/>
+      <c r="D35" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="30"/>
+      <c r="L35" s="27"/>
+      <c r="M35" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="N35" s="22"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="22"/>
+      <c r="Q35" s="22"/>
+      <c r="R35" s="30"/>
+    </row>
+    <row r="36" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C36" s="27"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="30"/>
+      <c r="L36" s="27"/>
+      <c r="M36" s="22"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="22"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="22"/>
+      <c r="R36" s="30"/>
+    </row>
+    <row r="37" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C37" s="27"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="30"/>
+      <c r="L37" s="27"/>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="22"/>
+      <c r="Q37" s="22"/>
+      <c r="R37" s="30"/>
+    </row>
+    <row r="38" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C38" s="27"/>
+      <c r="D38" s="17"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+      <c r="I38" s="28"/>
+      <c r="L38" s="27"/>
+      <c r="M38" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="N38" s="17"/>
+      <c r="O38" s="17"/>
+      <c r="P38" s="17"/>
+      <c r="Q38" s="17"/>
+      <c r="R38" s="28"/>
+    </row>
+    <row r="39" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="C39" s="27"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="28"/>
+      <c r="L39" s="27"/>
+      <c r="M39" s="17"/>
+      <c r="N39" s="17"/>
+      <c r="O39" s="17"/>
+      <c r="P39" s="17"/>
+      <c r="Q39" s="17"/>
+      <c r="R39" s="28"/>
+    </row>
+    <row r="40" spans="3:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C40" s="31"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="32"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="33"/>
+      <c r="L40" s="27"/>
+      <c r="M40" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="N40" s="17"/>
+      <c r="O40" s="17"/>
+      <c r="P40" s="17"/>
+      <c r="Q40" s="17"/>
+      <c r="R40" s="28"/>
+    </row>
+    <row r="41" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="L41" s="27"/>
+      <c r="M41" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+      <c r="R41" s="28"/>
+    </row>
+    <row r="42" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="L42" s="27"/>
+      <c r="M42" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="N42" s="17"/>
+      <c r="O42" s="17"/>
+      <c r="P42" s="17"/>
+      <c r="Q42" s="17"/>
+      <c r="R42" s="28"/>
+    </row>
+    <row r="43" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="L43" s="27"/>
+      <c r="M43" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="N43" s="17"/>
+      <c r="O43" s="17"/>
+      <c r="P43" s="17"/>
+      <c r="Q43" s="17"/>
+      <c r="R43" s="28"/>
+    </row>
+    <row r="44" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="L44" s="27"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17"/>
+      <c r="O44" s="17"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="17"/>
+      <c r="R44" s="28"/>
+    </row>
+    <row r="45" spans="3:18" x14ac:dyDescent="0.3">
+      <c r="L45" s="27"/>
+      <c r="M45" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="28"/>
+    </row>
+    <row r="46" spans="3:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L46" s="31"/>
+      <c r="M46" s="32"/>
+      <c r="N46" s="32"/>
+      <c r="O46" s="32"/>
+      <c r="P46" s="32"/>
+      <c r="Q46" s="32"/>
+      <c r="R46" s="33"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B32:G34"/>
-    <mergeCell ref="B15:G16"/>
+  <mergeCells count="6">
+    <mergeCell ref="D35:I37"/>
+    <mergeCell ref="D18:I19"/>
+    <mergeCell ref="M18:R19"/>
+    <mergeCell ref="M35:R37"/>
+    <mergeCell ref="N11:Q11"/>
+    <mergeCell ref="N15:P15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
